--- a/output/stock_quant_scores/LLY_balance_df.xlsx
+++ b/output/stock_quant_scores/LLY_balance_df.xlsx
@@ -1881,25 +1881,35 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>16884700000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>3399700000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>8979200000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>8958500000</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>39651200000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1913,7 +1923,9 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>15052700000</v>
+      </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1929,7 +1941,9 @@
         <v>495100000</v>
       </c>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>48806000000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
@@ -1953,10 +1967,14 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>18452400000</v>
+      </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>3886000000</v>
+      </c>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
@@ -1969,7 +1987,9 @@
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
+      <c r="CF6" t="n">
+        <v>3818500000</v>
+      </c>
       <c r="CG6" t="n">
         <v>2097900000</v>
       </c>
